--- a/Hindernislijst en materiaallijst.xlsx
+++ b/Hindernislijst en materiaallijst.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="KLZkFfNsmPN5ycAg47D6BnxxVIVg6V1d4p7FdXK00cQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="+2oxmww10mnQ9ZrBka2lEIjLYW6KINX/AxHpY7WI6o4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="216">
   <si>
     <t>Hindernislijst 2026</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Vrijwilliger 2</t>
   </si>
   <si>
-    <t>Vervangen door</t>
-  </si>
-  <si>
     <t>Wie bericht</t>
   </si>
   <si>
@@ -66,42 +63,39 @@
     <t>vast onderdeel Koppel</t>
   </si>
   <si>
+    <t>Glijplastic</t>
+  </si>
+  <si>
+    <t>Maurice</t>
+  </si>
+  <si>
+    <t>Duiker</t>
+  </si>
+  <si>
+    <t>Klimrek</t>
+  </si>
+  <si>
+    <t>Boomstammetjes</t>
+  </si>
+  <si>
+    <t>Slootdoorwading</t>
+  </si>
+  <si>
+    <t>Laat je rijden</t>
+  </si>
+  <si>
+    <t>incl. groepsfoto.</t>
+  </si>
+  <si>
+    <t>Bernd's special 1</t>
+  </si>
+  <si>
+    <t>Bernd's special 2</t>
+  </si>
+  <si>
     <t>Kruipnet</t>
   </si>
   <si>
-    <t>Glad plastic?</t>
-  </si>
-  <si>
-    <t>Maurice</t>
-  </si>
-  <si>
-    <t>Touwzwaai</t>
-  </si>
-  <si>
-    <t>Duiker</t>
-  </si>
-  <si>
-    <t>Klimrek</t>
-  </si>
-  <si>
-    <t>Boomstammetjes</t>
-  </si>
-  <si>
-    <t>Slootdoorwading</t>
-  </si>
-  <si>
-    <t>Laat je rijden</t>
-  </si>
-  <si>
-    <t>incl. groepsfoto.</t>
-  </si>
-  <si>
-    <t>Bernd's special 1</t>
-  </si>
-  <si>
-    <t>Bernd's special 2</t>
-  </si>
-  <si>
     <t>Sandwood special</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>Verticaal Net</t>
   </si>
   <si>
-    <t>Wip-Wap</t>
-  </si>
-  <si>
     <t>Loopbrug</t>
   </si>
   <si>
@@ -327,18 +318,9 @@
     <t>Opruimen na afloop Koppel</t>
   </si>
   <si>
-    <t>Larna Hiddink</t>
-  </si>
-  <si>
-    <t>Marleen Blok</t>
-  </si>
-  <si>
     <t>Opruimen na afloop bos</t>
   </si>
   <si>
-    <t>Koen Jansen</t>
-  </si>
-  <si>
     <t>Materiaallijst 2026</t>
   </si>
   <si>
@@ -369,120 +351,123 @@
     <t>nvt</t>
   </si>
   <si>
+    <t>Landbouwplastic incl. bevstigingsmateriaal</t>
+  </si>
+  <si>
     <t>Erwin</t>
   </si>
   <si>
     <t>Rob Alink</t>
   </si>
   <si>
+    <t>Groenezeep</t>
+  </si>
+  <si>
+    <t>spanbanden</t>
+  </si>
+  <si>
+    <t>Touw (bij begin)</t>
+  </si>
+  <si>
+    <t>Houten pallet (bij einde)</t>
+  </si>
+  <si>
+    <t>Bindtouw (voor pallet)</t>
+  </si>
+  <si>
+    <t>Piketpaaltjes (voor pallet)</t>
+  </si>
+  <si>
+    <t>Brandweerauto</t>
+  </si>
+  <si>
+    <t>Bernd Veldhuis</t>
+  </si>
+  <si>
     <t>Piketpaaltjes</t>
   </si>
   <si>
+    <t>Huub</t>
+  </si>
+  <si>
+    <t>Klimnet</t>
+  </si>
+  <si>
+    <t>Neede</t>
+  </si>
+  <si>
+    <t>Balk 6m</t>
+  </si>
+  <si>
+    <t>Sjorbanden</t>
+  </si>
+  <si>
+    <t>Bindtouw</t>
+  </si>
+  <si>
+    <t>Meterpalen</t>
+  </si>
+  <si>
+    <t>Palen met klompen</t>
+  </si>
+  <si>
+    <t>WC-brillen</t>
+  </si>
+  <si>
+    <t>Balk 4m</t>
+  </si>
+  <si>
+    <t>Huub Stegenman</t>
+  </si>
+  <si>
+    <t>Bokje</t>
+  </si>
+  <si>
+    <t>Langemat</t>
+  </si>
+  <si>
+    <t>Blokmat</t>
+  </si>
+  <si>
+    <t>Ton</t>
+  </si>
+  <si>
+    <t>Prikstokje</t>
+  </si>
+  <si>
+    <t>Verkeerslint</t>
+  </si>
+  <si>
+    <t>70m</t>
+  </si>
+  <si>
+    <t>Hok Nooit Gedacht</t>
+  </si>
+  <si>
+    <t>Slootnet</t>
+  </si>
+  <si>
+    <t>Balk 4-6m</t>
+  </si>
+  <si>
+    <t>Bierkratjes</t>
+  </si>
+  <si>
+    <t>Klimnet (2-3m lang)</t>
+  </si>
+  <si>
+    <t>Paal</t>
+  </si>
+  <si>
+    <t>Touw</t>
+  </si>
+  <si>
+    <t>Peter Stegeman</t>
+  </si>
+  <si>
     <t>?</t>
   </si>
   <si>
-    <t>Landbouwplastic incl. bevstigingsmateriaal</t>
-  </si>
-  <si>
-    <t>spanbanden</t>
-  </si>
-  <si>
-    <t>Touw (bij begin)</t>
-  </si>
-  <si>
-    <t>Houten pallet (bij einde)</t>
-  </si>
-  <si>
-    <t>Bindtouw (voor pallet)</t>
-  </si>
-  <si>
-    <t>Piketpaaltjes (voor pallet)</t>
-  </si>
-  <si>
-    <t>Bernd Veldhuis</t>
-  </si>
-  <si>
-    <t>Klimnet</t>
-  </si>
-  <si>
-    <t>Balk 6m</t>
-  </si>
-  <si>
-    <t>Sjorbanden</t>
-  </si>
-  <si>
-    <t>Bindtouw</t>
-  </si>
-  <si>
-    <t>Meterpalen</t>
-  </si>
-  <si>
-    <t>Palen met klompen</t>
-  </si>
-  <si>
-    <t>WC-brillen</t>
-  </si>
-  <si>
-    <t>Balk 4m</t>
-  </si>
-  <si>
-    <t>Huub</t>
-  </si>
-  <si>
-    <t>Bokje</t>
-  </si>
-  <si>
-    <t>Langemat</t>
-  </si>
-  <si>
-    <t>Huub Stegenman</t>
-  </si>
-  <si>
-    <t>Blokmat</t>
-  </si>
-  <si>
-    <t>Ton</t>
-  </si>
-  <si>
-    <t>Prikstokje</t>
-  </si>
-  <si>
-    <t>Verkeerslint</t>
-  </si>
-  <si>
-    <t>70m</t>
-  </si>
-  <si>
-    <t>Hok Nooit Gedacht</t>
-  </si>
-  <si>
-    <t>Slootnet</t>
-  </si>
-  <si>
-    <t>Balk 4-6m</t>
-  </si>
-  <si>
-    <t>Lianenbrug</t>
-  </si>
-  <si>
-    <t>Touw met lusjes</t>
-  </si>
-  <si>
-    <t>Tiewraps</t>
-  </si>
-  <si>
-    <t>Klimnet (2-3m lang)</t>
-  </si>
-  <si>
-    <t>Paal</t>
-  </si>
-  <si>
-    <t>Touw</t>
-  </si>
-  <si>
-    <t>Peter Stegeman</t>
-  </si>
-  <si>
     <t>Pallets</t>
   </si>
   <si>
@@ -513,21 +498,36 @@
     <t>Martijn</t>
   </si>
   <si>
+    <t>Ladder</t>
+  </si>
+  <si>
     <t>Brug af - Brug op</t>
   </si>
   <si>
+    <t>Balk</t>
+  </si>
+  <si>
+    <t>Bruf af - Brug op</t>
+  </si>
+  <si>
+    <t>Ponton</t>
+  </si>
+  <si>
+    <t>Uitklimmen</t>
+  </si>
+  <si>
+    <t>Inklimment</t>
+  </si>
+  <si>
+    <t>Meterpaaltjes</t>
+  </si>
+  <si>
+    <t>Voor bevestigen pallet</t>
+  </si>
+  <si>
     <t>Boomslinger</t>
   </si>
   <si>
-    <t>Klimnet (2-3m lang) (uitklim)</t>
-  </si>
-  <si>
-    <t>Meterpaaltjes</t>
-  </si>
-  <si>
-    <t>Onzeker of deze gebruikt worden</t>
-  </si>
-  <si>
     <t>Martijn Janzen</t>
   </si>
   <si>
@@ -540,25 +540,13 @@
     <t>Stokken</t>
   </si>
   <si>
-    <t>In de Ton</t>
-  </si>
-  <si>
-    <t>pittenzakken</t>
-  </si>
-  <si>
-    <t>kruiwagen</t>
-  </si>
-  <si>
-    <t>Touw plus bevestigingsmateriaal</t>
-  </si>
-  <si>
     <t>Palen 2m</t>
   </si>
   <si>
     <t>Palen 3m</t>
   </si>
   <si>
-    <t>Tim</t>
+    <t>Arjen Bloemendaal</t>
   </si>
   <si>
     <t>Vrachtwagen</t>
@@ -570,9 +558,15 @@
     <t>sproeier</t>
   </si>
   <si>
+    <t>Zondag</t>
+  </si>
+  <si>
     <t>Finish Boog</t>
   </si>
   <si>
+    <t>Finishboog</t>
+  </si>
+  <si>
     <t>Materiaal overigens</t>
   </si>
   <si>
@@ -595,9 +589,6 @@
   </si>
   <si>
     <t>50m</t>
-  </si>
-  <si>
-    <t>BouwTeams</t>
   </si>
   <si>
     <t>Bouwhoofd</t>
@@ -685,7 +676,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -722,11 +713,6 @@
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -871,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -905,10 +891,10 @@
     <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -922,10 +908,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -938,9 +924,6 @@
     </xf>
     <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -960,13 +943,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -976,21 +955,17 @@
     <xf borderId="0" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="12" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="13" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="2" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1000,15 +975,16 @@
     <xf borderId="2" fillId="14" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="12" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="11" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="11" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="14" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1023,28 +999,31 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1308,13 +1287,13 @@
     <col customWidth="1" min="2" max="2" width="25.57"/>
     <col customWidth="1" min="3" max="3" width="3.57"/>
     <col customWidth="1" min="4" max="4" width="2.43"/>
-    <col customWidth="1" min="5" max="6" width="30.14"/>
-    <col customWidth="1" min="7" max="7" width="20.71"/>
-    <col customWidth="1" hidden="1" min="8" max="9" width="13.86"/>
-    <col customWidth="1" hidden="1" min="10" max="10" width="19.57"/>
-    <col customWidth="1" min="11" max="11" width="8.71"/>
-    <col customWidth="1" min="12" max="12" width="40.29"/>
-    <col customWidth="1" min="13" max="28" width="8.71"/>
+    <col customWidth="1" min="5" max="5" width="30.14"/>
+    <col customWidth="1" min="6" max="6" width="20.71"/>
+    <col customWidth="1" hidden="1" min="7" max="8" width="13.86"/>
+    <col customWidth="1" hidden="1" min="9" max="9" width="19.57"/>
+    <col customWidth="1" min="10" max="10" width="8.71"/>
+    <col customWidth="1" min="11" max="11" width="40.29"/>
+    <col customWidth="1" min="12" max="27" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -1343,7 +1322,7 @@
       <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -1355,9 +1334,7 @@
       <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1374,241 +1351,243 @@
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2">
         <v>1.0</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="10"/>
+      <c r="J3" s="10"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2">
         <v>2.0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8"/>
+      <c r="H4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2">
         <v>3.0</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="10"/>
+      <c r="H5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2">
         <v>4.0</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="8" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="14"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2">
         <v>5.0</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="E7" s="14"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="10"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2">
         <v>6.0</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2">
         <v>7.0</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2">
         <v>8.0</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="17">
-        <v>9.0</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>11</v>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="22"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
       <c r="N11" s="21"/>
@@ -1625,93 +1604,76 @@
       <c r="Y11" s="21"/>
       <c r="Z11" s="21"/>
       <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="23">
+      <c r="A12" s="2">
         <v>10.0</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>26</v>
+      <c r="B12" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
+      <c r="H12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="10"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2">
         <v>11.0</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="10"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2">
         <v>12.0</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="10"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2">
@@ -1721,96 +1683,87 @@
         <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="E15" s="8"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="10"/>
+      <c r="G15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2">
         <v>14.0</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="10"/>
+      <c r="G16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2">
         <v>15.0</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="26" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="26" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2">
         <v>16.0</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>33</v>
+      <c r="B18" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>32</v>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="24"/>
+      <c r="J18" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -1818,77 +1771,83 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
-      <c r="K19" s="26"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="24"/>
+      <c r="J19" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2">
         <v>18.0</v>
       </c>
       <c r="B20" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="24"/>
+      <c r="J20" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
-      <c r="K20" s="26"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="17">
-        <v>19.0</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>36</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
-      <c r="K21" s="26"/>
+      <c r="H21" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="23">
+      <c r="A22" s="2">
         <v>20.0</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>37</v>
+      <c r="B22" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>32</v>
+      <c r="H22" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -1896,23 +1855,23 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="E23" s="12"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>32</v>
+      <c r="G23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -1924,72 +1883,66 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="26" t="s">
-        <v>32</v>
-      </c>
+      <c r="H24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2">
         <v>23.0</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="11"/>
+        <v>10</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2">
         <v>24.0</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="13"/>
-      <c r="K26" s="26" t="s">
-        <v>32</v>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -1997,23 +1950,21 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K27" s="26" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -2021,22 +1972,22 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="26" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -2044,23 +1995,23 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K29" s="26" t="s">
-        <v>32</v>
+      <c r="H29" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
@@ -2068,183 +2019,178 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="13"/>
-      <c r="K30" s="26" t="s">
-        <v>32</v>
+      <c r="H30" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="17">
+      <c r="A31" s="2">
         <v>29.0</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>47</v>
+      <c r="B31" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="K31" s="26" t="s">
-        <v>32</v>
+      <c r="G31" s="9"/>
+      <c r="H31" s="14"/>
+      <c r="J31" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="23">
+      <c r="A32" s="2">
         <v>30.0</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>48</v>
+      <c r="B32" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="E32" s="14"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="14"/>
-      <c r="K32" s="26"/>
+      <c r="G32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2">
         <v>31.0</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>49</v>
+      <c r="B33" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="2" t="str">
+        <f>D32</f>
+        <v>x</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="30" t="s">
         <v>11</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="K33" s="26" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2">
         <v>32.0</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>50</v>
+      <c r="B34" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="2" t="str">
-        <f>D33</f>
-        <v>x</v>
-      </c>
-      <c r="E34" s="11"/>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="33" t="s">
-        <v>12</v>
+      <c r="G34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2">
         <v>33.0</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>22</v>
+      <c r="B35" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K35" s="33" t="s">
-        <v>12</v>
+      <c r="G35" s="9"/>
+      <c r="H35" s="8"/>
+      <c r="J35" s="30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2">
         <v>34.0</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>52</v>
+      <c r="B36" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8"/>
-      <c r="K36" s="33"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2">
         <v>35.0</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="13"/>
-      <c r="K37" s="33" t="s">
-        <v>12</v>
+      <c r="H37" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -2252,23 +2198,22 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="32"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J38" s="30" t="s">
         <v>11</v>
-      </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I38" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="K38" s="33" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -2276,23 +2221,24 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J39" s="30" t="s">
         <v>11</v>
-      </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="K39" s="33" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -2300,78 +2246,79 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J41" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="2" t="s">
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I42" s="13"/>
+      <c r="J42" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K40" s="33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="17">
-        <v>39.0</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="J41" s="13"/>
-      <c r="K41" s="33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="23">
-        <v>40.0</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="8" t="s">
+      <c r="K42" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="K42" s="33" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -2382,535 +2329,476 @@
         <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="H43" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J43" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" s="14" t="s">
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J43" s="13"/>
-      <c r="K43" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="2">
-        <v>42.0</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K44" s="33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="8"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="D46" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="I46" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J46" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="35"/>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="13"/>
+      <c r="B47" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D47" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38" t="s">
+      <c r="F47" s="8"/>
+      <c r="G47" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="H47" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="I47" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="J47" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
-      <c r="N47" s="39"/>
-      <c r="O47" s="39"/>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="39"/>
-      <c r="S47" s="39"/>
-      <c r="T47" s="39"/>
-      <c r="U47" s="39"/>
-      <c r="V47" s="39"/>
-      <c r="W47" s="39"/>
-      <c r="X47" s="39"/>
-      <c r="Y47" s="39"/>
-      <c r="Z47" s="39"/>
-      <c r="AA47" s="39"/>
-      <c r="AB47" s="39"/>
+      <c r="K47" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="13"/>
       <c r="B48" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="F48" s="41"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="K48" s="42" t="s">
+      <c r="E48" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="F48" s="36"/>
+      <c r="G48" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="36" t="s">
         <v>71</v>
       </c>
+      <c r="J48" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="K48" s="36"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="B49" s="36" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="F49" s="44"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J49" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="K49" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="L49" s="36"/>
+      <c r="E49" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="36"/>
+      <c r="G49" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="38" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="B50" s="36" t="s">
-        <v>72</v>
-      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="44"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="K50" s="42" t="s">
-        <v>70</v>
-      </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="36"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
+      <c r="B51" s="36"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="41"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="B52" s="36"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="46"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="41"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="B53" s="36"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K53" s="46"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
+      <c r="B54" s="36" t="s">
+        <v>73</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
+      <c r="E54" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G54" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" s="42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="B55" s="36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="40" t="s">
+      <c r="E55" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F55" s="41"/>
-      <c r="G55" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H55" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="K55" s="47" t="s">
-        <v>12</v>
+      <c r="G55" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J55" s="42" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="B56" s="36" t="s">
-        <v>76</v>
-      </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="F56" s="41"/>
-      <c r="G56" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H56" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="K56" s="47" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
+      <c r="B57" s="36" t="s">
+        <v>78</v>
+      </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
+      <c r="E57" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="B58" s="36" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="F58" s="41"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" s="47" t="s">
-        <v>12</v>
+      <c r="E58" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="G58" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="B59" s="36" t="s">
-        <v>81</v>
-      </c>
+      <c r="B59" s="36"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59" s="41"/>
-      <c r="H59" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" s="47" t="s">
-        <v>12</v>
-      </c>
+      <c r="E59" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="41"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="B60" s="36"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="F60" s="41"/>
-      <c r="H60" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" s="46"/>
+      <c r="E60" s="36"/>
+      <c r="G60" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" s="41"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="B61" s="36"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="H61" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K61" s="46"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
+      <c r="B62" s="36" t="s">
+        <v>82</v>
+      </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
+      <c r="E62" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="G62" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J62" s="38" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="B63" s="36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="F63" s="41"/>
-      <c r="H63" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="K63" s="42" t="s">
-        <v>70</v>
+      <c r="E63" s="36"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" s="38" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="B64" s="36" t="s">
-        <v>85</v>
-      </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" s="42" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
+      <c r="B65" s="36" t="s">
+        <v>84</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
+      <c r="E65" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G65" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" s="38" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="B66" s="36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="F66" s="41"/>
-      <c r="H66" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="42" t="s">
-        <v>70</v>
-      </c>
+      <c r="E66" s="44"/>
+      <c r="G66" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="K66" s="45"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="B67" s="36" t="s">
-        <v>87</v>
-      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="49"/>
-      <c r="H67" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K67" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="L67" s="32"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
+      <c r="B68" s="36" t="s">
+        <v>86</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
+      <c r="E68" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F68" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G68" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="B69" s="36" t="s">
-        <v>89</v>
-      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H69" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K69" s="47" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
+      <c r="B70" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
+      <c r="E70" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="J70" s="42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="B71" s="11" t="s">
-        <v>92</v>
+      <c r="B71" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="F71" s="50"/>
-      <c r="G71" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
-      <c r="K71" s="47" t="s">
-        <v>12</v>
+      <c r="E71" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="B72" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K72" s="47" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
+      <c r="B73" s="12" t="s">
+        <v>93</v>
+      </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
+      <c r="E73" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="B74" s="11" t="s">
-        <v>96</v>
+      <c r="B74" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F74" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K74" s="47" t="s">
-        <v>12</v>
+      <c r="J74" s="47" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="B75" s="11" t="s">
-        <v>96</v>
-      </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K75" s="51" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
+      <c r="E76" s="12"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="B77" s="11" t="s">
-        <v>101</v>
-      </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F77" s="11"/>
+      <c r="E77" s="12"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F78" s="11"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
+      <c r="B79" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
+      <c r="E79" s="12"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="B80" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F80" s="11"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="C81" s="2"/>
@@ -6540,13 +6428,9 @@
       <c r="C987" s="2"/>
       <c r="D987" s="2"/>
     </row>
-    <row r="988" ht="14.25" customHeight="1">
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="Doolhof" location="Doolhof!A1" ref="B20"/>
+    <hyperlink display="Doolhof" location="Doolhof!A1" ref="B19"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
@@ -6573,661 +6457,686 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="G2" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="54" t="s">
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="D3" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="G3" s="53"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="54">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="D4" s="54">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F4" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G4" s="53"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="54">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="56">
+      <c r="D5" s="54">
         <v>1.0</v>
       </c>
-      <c r="B3" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="56">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="57"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="56">
+      <c r="E5" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="54">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="52">
         <v>2.0</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="57"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="59">
-        <v>4.0</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="56">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="56">
-        <v>6.0</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="57"/>
+      <c r="E6" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="56">
+        <v>3.0</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="58">
+        <v>2.0</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="54">
         <v>4.0</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B8" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="54">
+        <v>5.0</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="B10" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C10" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="54">
+        <v>7.0</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="54">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="54">
+        <v>8.0</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="56">
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="54">
+        <v>9.0</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="54">
+        <v>10.0</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="53"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="54">
+        <v>10.0</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="54">
+        <v>4.0</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="54">
+        <v>11.0</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="53"/>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="54">
+        <v>12.0</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="52">
         <v>2.0</v>
       </c>
-      <c r="E7" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="57"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="60">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="60">
+      <c r="E20" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" s="53"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="54">
+        <v>12.0</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="54">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="52">
         <v>2.0</v>
       </c>
-      <c r="E8" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="56">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="56">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="57"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="56">
+      <c r="E22" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="54">
+        <v>12.0</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="54">
+        <v>12.0</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="54">
+        <v>13.0</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E25" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="53"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="54">
+        <v>13.0</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="54">
+        <v>14.0</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="52">
         <v>6.0</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="56">
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="57"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="56">
-        <v>7.0</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="57" t="s">
+      <c r="E27" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="53"/>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="54">
+        <v>14.0</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E28" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="54">
+        <v>15.0</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="54">
+        <v>2.0</v>
+      </c>
+      <c r="E29" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="56">
+      <c r="F29" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" s="53"/>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="54">
+        <v>15.0</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="54">
+        <v>2.0</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="54">
+        <v>16.0</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="52">
         <v>1.0</v>
       </c>
-      <c r="E11" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="57"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="56">
-        <v>7.0</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="56">
-        <v>7.0</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="56">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E14" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="56">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G15" s="57"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="56">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="57"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="56">
-        <v>9.0</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G17" s="57"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="56">
-        <v>10.0</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E18" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="57"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="56">
-        <v>10.0</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="59">
-        <v>4.0</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="56">
-        <v>11.0</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G20" s="57"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E21" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" s="57"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E23" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="B24" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E24" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="B25" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="56">
-        <v>13.0</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="57" t="s">
+      <c r="E31" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E26" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F26" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="57"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="56">
-        <v>13.0</v>
-      </c>
-      <c r="B27" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E27" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="56">
-        <v>14.0</v>
-      </c>
-      <c r="B28" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" s="56">
-        <v>6.0</v>
-      </c>
-      <c r="E28" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="57"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="56">
-        <v>14.0</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E29" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="56"/>
-      <c r="B30" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="E30" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="56"/>
-      <c r="B31" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="E31" s="58" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
+      <c r="G31" s="53"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="56">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="B32" s="57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="56">
+        <v>135</v>
+      </c>
+      <c r="D32" s="58">
+        <v>2.0</v>
+      </c>
+      <c r="E32" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="19"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="56">
+        <v>16.0</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="58">
         <v>1.0</v>
       </c>
-      <c r="E32" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F32" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="57"/>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="60">
-        <v>15.0</v>
-      </c>
-      <c r="B33" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="61" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" s="60">
-        <v>2.0</v>
-      </c>
-      <c r="E33" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
+      <c r="E33" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -7249,23 +7158,25 @@
       <c r="Z33" s="19"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="60">
-        <v>15.0</v>
-      </c>
-      <c r="B34" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="60">
-        <v>1.0</v>
-      </c>
-      <c r="E34" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
+      <c r="A34" s="56">
+        <v>17.0</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="56">
+        <v>64.0</v>
+      </c>
+      <c r="E34" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G34" s="57"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -7287,21 +7198,23 @@
       <c r="Z34" s="19"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="60"/>
-      <c r="B35" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="63">
-        <v>64.0</v>
-      </c>
-      <c r="E35" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
+      <c r="A35" s="56">
+        <v>17.0</v>
+      </c>
+      <c r="B35" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -7323,21 +7236,25 @@
       <c r="Z35" s="19"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="60"/>
-      <c r="B36" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="62" t="s">
+      <c r="A36" s="56">
+        <v>18.0</v>
+      </c>
+      <c r="B36" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
+      <c r="D36" s="56">
+        <v>1.0</v>
+      </c>
+      <c r="E36" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="57"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -7359,21 +7276,23 @@
       <c r="Z36" s="19"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="60"/>
-      <c r="B37" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="63">
+      <c r="A37" s="56">
+        <v>18.0</v>
+      </c>
+      <c r="B37" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="56">
         <v>1.0</v>
       </c>
-      <c r="E37" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
+      <c r="E37" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -7395,13 +7314,25 @@
       <c r="Z37" s="19"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="60"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
+      <c r="A38" s="56">
+        <v>19.0</v>
+      </c>
+      <c r="B38" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" s="56">
+        <v>10.0</v>
+      </c>
+      <c r="E38" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G38" s="57"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -7423,539 +7354,556 @@
       <c r="Z38" s="19"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="56">
-        <v>16.0</v>
-      </c>
-      <c r="B39" s="57" t="s">
+      <c r="A39" s="54">
+        <v>20.0</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E39" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="53"/>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="54">
+        <v>20.0</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="54">
+        <v>20.0</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E41" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="54">
+        <v>21.0</v>
+      </c>
+      <c r="B42" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E42" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="C39" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" s="56">
+      <c r="G42" s="53"/>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="54">
+        <v>21.0</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="52">
+        <v>4.0</v>
+      </c>
+      <c r="E43" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="54">
+        <v>21.0</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E44" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="54">
+        <v>22.0</v>
+      </c>
+      <c r="B45" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="52">
         <v>1.0</v>
       </c>
-      <c r="E39" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39" s="57"/>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="56">
-        <v>16.0</v>
-      </c>
-      <c r="B40" s="57" t="s">
+      <c r="E45" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C40" s="57" t="s">
+      <c r="G45" s="53"/>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="54">
+        <v>22.0</v>
+      </c>
+      <c r="B46" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="54">
+        <v>23.0</v>
+      </c>
+      <c r="B47" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E47" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G47" s="53"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="A48" s="54">
+        <v>23.0</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E48" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="A49" s="54">
+        <v>24.0</v>
+      </c>
+      <c r="B49" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E49" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="D40" s="56">
-        <v>8.0</v>
-      </c>
-      <c r="E40" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="56">
-        <v>16.0</v>
-      </c>
-      <c r="B41" s="57" t="s">
+      <c r="F49" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G49" s="53"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="A50" s="54">
+        <v>24.0</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
+      <c r="A51" s="54">
+        <v>24.0</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
+      <c r="A52" s="54">
+        <v>25.0</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="52"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="G52" s="53"/>
+    </row>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" s="54">
+        <v>26.0</v>
+      </c>
+      <c r="B53" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="G53" s="53"/>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="A54" s="54">
+        <v>26.0</v>
+      </c>
+      <c r="B54" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="54">
+        <v>26.0</v>
+      </c>
+      <c r="B55" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="D41" s="56">
-        <v>8.0</v>
-      </c>
-      <c r="E41" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="56">
-        <v>17.0</v>
-      </c>
-      <c r="B42" s="57" t="s">
+      <c r="D55" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E55" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1">
+      <c r="A56" s="54">
+        <v>26.0</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E56" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+    </row>
+    <row r="57" ht="14.25" customHeight="1">
+      <c r="A57" s="54">
+        <v>27.0</v>
+      </c>
+      <c r="B57" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E57" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" s="53"/>
+    </row>
+    <row r="58" ht="14.25" customHeight="1">
+      <c r="A58" s="54">
+        <v>27.0</v>
+      </c>
+      <c r="B58" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="D58" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E58" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="56">
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+    </row>
+    <row r="59" ht="14.25" customHeight="1">
+      <c r="A59" s="54">
+        <v>28.0</v>
+      </c>
+      <c r="B59" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="52">
+        <v>10.0</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="G59" s="53"/>
+    </row>
+    <row r="60" ht="14.25" customHeight="1">
+      <c r="A60" s="54">
+        <v>28.0</v>
+      </c>
+      <c r="B60" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+    </row>
+    <row r="61" ht="14.25" customHeight="1">
+      <c r="A61" s="54">
+        <v>28.0</v>
+      </c>
+      <c r="B61" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" s="52">
         <v>1.0</v>
       </c>
-      <c r="E42" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="G42" s="57"/>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="56">
-        <v>17.0</v>
-      </c>
-      <c r="B43" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" s="56">
+      <c r="E61" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+    </row>
+    <row r="62" ht="14.25" customHeight="1">
+      <c r="A62" s="54">
+        <v>29.0</v>
+      </c>
+      <c r="B62" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" s="54">
         <v>1.0</v>
       </c>
-      <c r="E43" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="56">
-        <v>17.0</v>
-      </c>
-      <c r="B44" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E44" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="56">
-        <v>18.0</v>
-      </c>
-      <c r="B45" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E45" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F45" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="G45" s="57"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="56">
-        <v>18.0</v>
-      </c>
-      <c r="B46" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46" s="56">
-        <v>4.0</v>
-      </c>
-      <c r="E46" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="56">
-        <v>18.0</v>
-      </c>
-      <c r="B47" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="D47" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E47" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="56">
-        <v>19.0</v>
-      </c>
-      <c r="B48" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="D48" s="56">
+      <c r="E62" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+    </row>
+    <row r="63" ht="14.25" customHeight="1">
+      <c r="A63" s="54">
+        <v>29.0</v>
+      </c>
+      <c r="B63" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="54">
         <v>1.0</v>
       </c>
-      <c r="E48" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="G48" s="57"/>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="56">
-        <v>19.0</v>
-      </c>
-      <c r="B49" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E49" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="56">
-        <v>20.0</v>
-      </c>
-      <c r="B50" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E50" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F50" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" s="57"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="56">
-        <v>20.0</v>
-      </c>
-      <c r="B51" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C51" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E51" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="56">
-        <v>21.0</v>
-      </c>
-      <c r="B52" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E52" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F52" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G52" s="57"/>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="56">
-        <v>21.0</v>
-      </c>
-      <c r="B53" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E53" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="56">
-        <v>21.0</v>
-      </c>
-      <c r="B54" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="D54" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E54" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="56">
-        <v>22.0</v>
-      </c>
-      <c r="B55" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="56"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G55" s="57"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="56">
-        <v>23.0</v>
-      </c>
-      <c r="B56" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E56" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F56" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="G56" s="57"/>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="56">
-        <v>23.0</v>
-      </c>
-      <c r="B57" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E57" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="56">
-        <v>23.0</v>
-      </c>
-      <c r="B58" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E58" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="56">
-        <v>23.0</v>
-      </c>
-      <c r="B59" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>161</v>
-      </c>
-      <c r="D59" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E59" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="56">
-        <v>24.0</v>
-      </c>
-      <c r="B60" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="D60" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E60" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="G60" s="57"/>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="56">
-        <v>24.0</v>
-      </c>
-      <c r="B61" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="D61" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E61" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="56">
-        <v>25.0</v>
-      </c>
-      <c r="B62" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="D62" s="56">
-        <v>10.0</v>
-      </c>
-      <c r="E62" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="G62" s="57"/>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="56">
-        <v>25.0</v>
-      </c>
-      <c r="B63" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="D63" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E63" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
+      <c r="E63" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="56">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="B64" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" s="56">
+        <v>160</v>
+      </c>
+      <c r="C64" s="59" t="s">
+        <v>161</v>
+      </c>
+      <c r="D64" s="58">
         <v>1.0</v>
       </c>
-      <c r="E64" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="F64" s="57"/>
+      <c r="E64" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="55" t="s">
+        <v>153</v>
+      </c>
       <c r="G64" s="57"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="19"/>
+      <c r="W64" s="19"/>
+      <c r="X64" s="19"/>
+      <c r="Y64" s="19"/>
+      <c r="Z64" s="19"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="63">
-        <v>26.0</v>
-      </c>
-      <c r="B65" s="61" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65" s="60">
+      <c r="A65" s="56">
+        <v>30.0</v>
+      </c>
+      <c r="B65" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" s="56">
         <v>1.0</v>
       </c>
-      <c r="E65" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F65" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G65" s="61"/>
+      <c r="E65" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="19"/>
@@ -7977,23 +7925,23 @@
       <c r="Z65" s="19"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="63">
-        <v>26.0</v>
-      </c>
-      <c r="B66" s="61" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D66" s="60">
+      <c r="A66" s="56">
+        <v>30.0</v>
+      </c>
+      <c r="B66" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="56">
         <v>1.0</v>
       </c>
-      <c r="E66" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
+      <c r="E66" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="19"/>
@@ -8015,547 +7963,646 @@
       <c r="Z66" s="19"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="59">
-        <v>27.0</v>
-      </c>
-      <c r="B67" s="57" t="s">
+      <c r="A67" s="56">
+        <v>30.0</v>
+      </c>
+      <c r="B67" s="59" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="56">
+        <v>2.0</v>
+      </c>
+      <c r="E67" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="19"/>
+      <c r="O67" s="19"/>
+      <c r="P67" s="19"/>
+      <c r="Q67" s="19"/>
+      <c r="R67" s="19"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="19"/>
+      <c r="U67" s="19"/>
+      <c r="V67" s="19"/>
+      <c r="W67" s="19"/>
+      <c r="X67" s="19"/>
+      <c r="Y67" s="19"/>
+      <c r="Z67" s="19"/>
+    </row>
+    <row r="68" ht="14.25" customHeight="1">
+      <c r="A68" s="56">
+        <v>31.0</v>
+      </c>
+      <c r="B68" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="D68" s="56">
+        <v>2.0</v>
+      </c>
+      <c r="E68" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="19"/>
+      <c r="M68" s="19"/>
+      <c r="N68" s="19"/>
+      <c r="O68" s="19"/>
+      <c r="P68" s="19"/>
+      <c r="Q68" s="19"/>
+      <c r="R68" s="19"/>
+      <c r="S68" s="19"/>
+      <c r="T68" s="19"/>
+      <c r="U68" s="19"/>
+      <c r="V68" s="19"/>
+      <c r="W68" s="19"/>
+      <c r="X68" s="19"/>
+      <c r="Y68" s="19"/>
+      <c r="Z68" s="19"/>
+    </row>
+    <row r="69" ht="14.25" customHeight="1">
+      <c r="A69" s="56">
+        <v>31.0</v>
+      </c>
+      <c r="B69" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="D69" s="56">
+        <v>1.0</v>
+      </c>
+      <c r="E69" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="19"/>
+      <c r="O69" s="19"/>
+      <c r="P69" s="19"/>
+      <c r="Q69" s="19"/>
+      <c r="R69" s="19"/>
+      <c r="S69" s="19"/>
+      <c r="T69" s="19"/>
+      <c r="U69" s="19"/>
+      <c r="V69" s="19"/>
+      <c r="W69" s="19"/>
+      <c r="X69" s="19"/>
+      <c r="Y69" s="19"/>
+      <c r="Z69" s="19"/>
+    </row>
+    <row r="70" ht="14.25" customHeight="1">
+      <c r="A70" s="54">
+        <v>32.0</v>
+      </c>
+      <c r="B70" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" s="54">
+        <v>2.0</v>
+      </c>
+      <c r="E70" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G70" s="55" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" customHeight="1">
+      <c r="A71" s="54">
+        <v>32.0</v>
+      </c>
+      <c r="B71" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D71" s="54">
+        <v>1.0</v>
+      </c>
+      <c r="E71" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F71" s="55"/>
+      <c r="G71" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="C67" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D67" s="56">
+    </row>
+    <row r="72" ht="14.25" customHeight="1">
+      <c r="A72" s="54">
+        <v>32.0</v>
+      </c>
+      <c r="B72" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="54">
         <v>1.0</v>
       </c>
-      <c r="E67" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F67" s="58" t="s">
+      <c r="E72" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" s="53"/>
+      <c r="G72" s="55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" customHeight="1">
+      <c r="A73" s="54">
+        <v>33.0</v>
+      </c>
+      <c r="B73" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D73" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
+    </row>
+    <row r="74" ht="14.25" customHeight="1">
+      <c r="A74" s="54">
+        <v>34.0</v>
+      </c>
+      <c r="B74" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D74" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E74" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F74" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G74" s="53"/>
+    </row>
+    <row r="75" ht="14.25" customHeight="1">
+      <c r="A75" s="54">
+        <v>34.0</v>
+      </c>
+      <c r="B75" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="D75" s="52">
+        <v>12.0</v>
+      </c>
+      <c r="E75" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+    </row>
+    <row r="76" ht="14.25" customHeight="1">
+      <c r="A76" s="54">
+        <v>34.0</v>
+      </c>
+      <c r="B76" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D76" s="52">
+        <v>12.0</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+    </row>
+    <row r="77" ht="14.25" customHeight="1">
+      <c r="A77" s="54">
+        <v>35.0</v>
+      </c>
+      <c r="B77" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E77" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F77" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G77" s="53"/>
+    </row>
+    <row r="78" ht="14.25" customHeight="1">
+      <c r="A78" s="54">
+        <v>35.0</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" s="52">
+        <v>2.0</v>
+      </c>
+      <c r="E78" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+    </row>
+    <row r="79" ht="14.25" customHeight="1">
+      <c r="A79" s="54">
+        <v>36.0</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D79" s="52">
+        <v>3.0</v>
+      </c>
+      <c r="E79" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F79" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G79" s="53"/>
+    </row>
+    <row r="80" ht="14.25" customHeight="1">
+      <c r="A80" s="54">
+        <v>36.0</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C80" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80" s="52">
+        <v>6.0</v>
+      </c>
+      <c r="E80" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+    </row>
+    <row r="81" ht="14.25" customHeight="1">
+      <c r="A81" s="54">
+        <v>37.0</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D81" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E81" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
+    </row>
+    <row r="82" ht="14.25" customHeight="1">
+      <c r="A82" s="54">
+        <v>38.0</v>
+      </c>
+      <c r="B82" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="52">
+        <v>4.0</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82" s="53"/>
+    </row>
+    <row r="83" ht="14.25" customHeight="1">
+      <c r="A83" s="54">
+        <v>38.0</v>
+      </c>
+      <c r="B83" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="52">
+        <v>4.0</v>
+      </c>
+      <c r="E83" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
+    </row>
+    <row r="84" ht="14.25" customHeight="1">
+      <c r="A84" s="54">
+        <v>39.0</v>
+      </c>
+      <c r="B84" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D84" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E84" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F84" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="53"/>
+    </row>
+    <row r="85" ht="14.25" customHeight="1">
+      <c r="A85" s="54">
+        <v>39.0</v>
+      </c>
+      <c r="B85" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D85" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E85" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1">
+      <c r="A86" s="54">
+        <v>39.0</v>
+      </c>
+      <c r="B86" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="D86" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E86" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+    </row>
+    <row r="87" ht="14.25" customHeight="1">
+      <c r="A87" s="54">
+        <v>39.0</v>
+      </c>
+      <c r="B87" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D87" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E87" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="54">
+        <v>40.0</v>
+      </c>
+      <c r="B88" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C88" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D88" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E88" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="G88" s="53"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="A89" s="54">
+        <v>41.0</v>
+      </c>
+      <c r="B89" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D89" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="E89" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="F89" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G89" s="53"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="60">
+        <v>42.0</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D90" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G67" s="57"/>
-    </row>
-    <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="59">
-        <v>28.0</v>
-      </c>
-      <c r="B68" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="D68" s="56">
+      <c r="F90" s="55" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" ht="14.25" customHeight="1">
+      <c r="D91" s="13"/>
+      <c r="E91" s="12"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D92" s="13"/>
+      <c r="E92" s="12"/>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="B93" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="13">
         <v>1.0</v>
       </c>
-      <c r="E68" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F68" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G68" s="57"/>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="59">
-        <v>28.0</v>
-      </c>
-      <c r="B69" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="D69" s="56">
+      <c r="E93" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c r="B94" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D94" s="13">
         <v>2.0</v>
       </c>
-      <c r="E69" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="B70" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D70" s="56">
+      <c r="E94" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="B95" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D95" s="13">
+        <v>200.0</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
+      <c r="B96" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D96" s="12">
         <v>2.0</v>
       </c>
-      <c r="E70" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F70" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G70" s="57"/>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="B71" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C71" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D71" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="E71" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="B72" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C72" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="D72" s="56">
-        <v>12.0</v>
-      </c>
-      <c r="E72" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="59">
-        <v>30.0</v>
-      </c>
-      <c r="B73" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="C73" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D73" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E73" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F73" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G73" s="57"/>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="59">
-        <v>30.0</v>
-      </c>
-      <c r="B74" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="C74" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="D74" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E74" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-    </row>
-    <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="59">
-        <v>31.0</v>
-      </c>
-      <c r="B75" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="C75" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="56">
-        <v>3.0</v>
-      </c>
-      <c r="E75" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F75" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G75" s="57"/>
-    </row>
-    <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="59">
-        <v>31.0</v>
-      </c>
-      <c r="B76" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="D76" s="56">
-        <v>6.0</v>
-      </c>
-      <c r="E76" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="B77" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="C77" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="56">
-        <v>20.0</v>
-      </c>
-      <c r="E77" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G77" s="57"/>
-    </row>
-    <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="B78" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="C78" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="D78" s="56">
-        <v>2.0</v>
-      </c>
-      <c r="E78" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-    </row>
-    <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="59">
-        <v>33.0</v>
-      </c>
-      <c r="B79" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C79" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="D79" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E79" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-    </row>
-    <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="59">
-        <v>34.0</v>
-      </c>
-      <c r="B80" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="C80" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="D80" s="56">
-        <v>4.0</v>
-      </c>
-      <c r="E80" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F80" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G80" s="57"/>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="59">
-        <v>34.0</v>
-      </c>
-      <c r="B81" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="C81" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="D81" s="56">
-        <v>4.0</v>
-      </c>
-      <c r="E81" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="59">
-        <v>35.0</v>
-      </c>
-      <c r="B82" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C82" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="D82" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E82" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="F82" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="G82" s="57"/>
-    </row>
-    <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="59">
-        <v>35.0</v>
-      </c>
-      <c r="B83" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C83" s="57" t="s">
-        <v>180</v>
-      </c>
-      <c r="D83" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E83" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57"/>
-    </row>
-    <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="59">
-        <v>35.0</v>
-      </c>
-      <c r="B84" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C84" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="D84" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E84" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F84" s="57"/>
-      <c r="G84" s="57"/>
-    </row>
-    <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="59">
-        <v>35.0</v>
-      </c>
-      <c r="B85" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C85" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="D85" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E85" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="F85" s="57"/>
-      <c r="G85" s="57"/>
-    </row>
-    <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="59">
-        <v>36.0</v>
-      </c>
-      <c r="B86" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D86" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E86" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="59">
-        <v>37.0</v>
-      </c>
-      <c r="B87" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="E87" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="F87" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="G87" s="57"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="13"/>
-      <c r="B88" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D88" s="13"/>
-      <c r="E88" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
-      <c r="D89" s="13"/>
-      <c r="E89" s="11"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="11"/>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
-      <c r="B91" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D91" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="B92" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D92" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="B93" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C93" s="11" t="s">
+      <c r="E96" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" ht="14.25" customHeight="1">
+      <c r="C97" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D93" s="13">
-        <v>200.0</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
-      <c r="B94" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C94" s="11" t="s">
+      <c r="D97" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D94" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="C95" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
-      <c r="C96" s="11"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="11"/>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
-      <c r="C97" s="11"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="11"/>
+      <c r="E97" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
+      <c r="C98" s="12"/>
       <c r="D98" s="13"/>
-      <c r="E98" s="11"/>
+      <c r="E98" s="12"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="11" t="s">
-        <v>192</v>
-      </c>
+      <c r="C99" s="12"/>
       <c r="D99" s="13"/>
-      <c r="E99" s="65"/>
-    </row>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
+      <c r="E99" s="12"/>
+    </row>
+    <row r="100" ht="14.25" customHeight="1">
+      <c r="D100" s="13"/>
+      <c r="E100" s="12"/>
+    </row>
+    <row r="101" ht="14.25" customHeight="1">
+      <c r="A101" s="12"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="62"/>
+    </row>
     <row r="102" ht="14.25" customHeight="1"/>
     <row r="103" ht="14.25" customHeight="1"/>
     <row r="104" ht="14.25" customHeight="1"/>
     <row r="105" ht="14.25" customHeight="1"/>
     <row r="106" ht="14.25" customHeight="1"/>
     <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1">
-      <c r="D108" s="13"/>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
-      <c r="D109" s="13"/>
-    </row>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
     <row r="110" ht="14.25" customHeight="1">
       <c r="D110" s="13"/>
     </row>
@@ -11238,13 +11285,19 @@
     <row r="1003" ht="14.25" customHeight="1">
       <c r="D1003" s="13"/>
     </row>
+    <row r="1004" ht="14.25" customHeight="1">
+      <c r="D1004" s="13"/>
+    </row>
+    <row r="1005" ht="14.25" customHeight="1">
+      <c r="D1005" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F3:F87">
-      <formula1>"Bernd Veldhuis,Marc Imhof,Martijn Janzen,Huub Stegenman,Jelte Warmink,Peter Stegeman,Rob Alink,ntb"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F3:F90">
+      <formula1>"Bernd Veldhuis,Arjen Bloemendaal,Martijn Janzen,Huub Stegenman,Jelte Warmink,Peter Stegeman,Rob Alink,ntb,Zondag"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E99">
-      <formula1>"niemand,Esther,Erwin,Rob,Maurice,Bernd,Peter,Djurre,Tim,?,Martijn,Huub,Nienke,Hok Nooit Gedacht"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E101">
+      <formula1>"niemand,Esther,Erwin,Rob,Maurice,Bernd,Peter,Djurre,Neede,?,Martijn,Huub,Nienke,Hok Nooit Gedacht"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -11269,125 +11322,125 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="62"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="65"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="11" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="68" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="E3" s="62"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D4" s="66" t="s">
         <v>200</v>
       </c>
-      <c r="E3" s="65"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="E4" s="62"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="62"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="C6" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="65"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="32" t="s">
+      <c r="D6" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="65"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="32" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="11" t="s">
+    <row r="8">
+      <c r="A8" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="68" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="11" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A7">
+      <formula1>"Bernd Veldhuis,Arjen Bloemendaal,Martijn Janzen,Nienke Luddinkhedde,Jelte Warmink,Peter Stegeman,Rob Alink,ntb"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A8">
       <formula1>"Bernd Veldhuis,Marc Imhof,Martijn Janzen,Huub Stegeman,Jelte Warmink,nvt,Peter Stegeman,Rob Alink,ntb"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E1:E5">
       <formula1>"niemand,Esther,Erwin,Rob,Maurice,Bernd,Peter,Djurre,Tim,?,Martijn,Huub,Nienke,Hok Nooit Gedacht"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A7">
-      <formula1>"Bernd Veldhuis,Marc Imhof,Martijn Janzen,Nienke Luddinkhedde,Jelte Warmink,Peter Stegeman,Rob Alink,ntb"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -11405,40 +11458,40 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>212</v>
+      <c r="A1" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="26">
         <v>15.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="s">
-        <v>109</v>
+      <c r="A3" s="26" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="27">
+      <c r="B4" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="26">
         <v>64.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>143</v>
+      <c r="B5" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
